--- a/H5509_V2/bin/Debug/Logs/202510/Log_20251023-220101.xlsx
+++ b/H5509_V2/bin/Debug/Logs/202510/Log_20251023-220101.xlsx
@@ -487,6 +487,12 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-10-23 22:05:15]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 HardwareGXN.GSNAxisController.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 149
+   在 HardwareGXN.GSNAxisController.InitCard() 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-10-24 09:26:20]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 HardwareGXN.GSNAxisController.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 149
    在 HardwareGXN.GSNAxisController.InitCard() 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 35</x:t>
@@ -3388,6 +3394,1728 @@
         <x:v>39</x:v>
       </x:c>
     </x:row>
+    <x:row r="182" spans="1:4">
+      <x:c r="A182" s="1">
+        <x:v>45954.3932881829</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:4">
+      <x:c r="A183" s="1">
+        <x:v>45954.3932893287</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D183" s="2" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:4">
+      <x:c r="A184" s="1">
+        <x:v>45954.3934253588</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:4">
+      <x:c r="A185" s="1">
+        <x:v>45954.3934994444</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:4">
+      <x:c r="A186" s="1">
+        <x:v>45954.3934997685</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:4">
+      <x:c r="A187" s="1">
+        <x:v>45954.3935001389</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:4">
+      <x:c r="A188" s="1">
+        <x:v>45954.3935004977</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:4">
+      <x:c r="A189" s="1">
+        <x:v>45954.3935008681</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:4">
+      <x:c r="A190" s="1">
+        <x:v>45954.3935012268</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:4">
+      <x:c r="A191" s="1">
+        <x:v>45954.3935015972</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:4">
+      <x:c r="A192" s="1">
+        <x:v>45954.393501956</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:4">
+      <x:c r="A193" s="1">
+        <x:v>45954.3935023264</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:4">
+      <x:c r="A194" s="1">
+        <x:v>45954.3935026852</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:4">
+      <x:c r="A195" s="1">
+        <x:v>45954.3935030556</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:4">
+      <x:c r="A196" s="1">
+        <x:v>45954.3935034144</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:4">
+      <x:c r="A197" s="1">
+        <x:v>45954.3935037847</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:4">
+      <x:c r="A198" s="1">
+        <x:v>45954.3935041551</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:4">
+      <x:c r="A199" s="1">
+        <x:v>45954.3935045139</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:4">
+      <x:c r="A200" s="1">
+        <x:v>45954.3935048843</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:4">
+      <x:c r="A201" s="1">
+        <x:v>45954.3935053241</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:4">
+      <x:c r="A202" s="1">
+        <x:v>45954.393505787</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C202" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D202" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:4">
+      <x:c r="A203" s="1">
+        <x:v>45954.3935061458</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C203" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D203" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:4">
+      <x:c r="A204" s="1">
+        <x:v>45954.3935064352</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D204" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:4">
+      <x:c r="A205" s="1">
+        <x:v>45954.393506875</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C205" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D205" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:4">
+      <x:c r="A206" s="1">
+        <x:v>45954.3935072338</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C206" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D206" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:4">
+      <x:c r="A207" s="1">
+        <x:v>45954.3935076042</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C207" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D207" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:4">
+      <x:c r="A208" s="1">
+        <x:v>45954.3935079514</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C208" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D208" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:4">
+      <x:c r="A209" s="1">
+        <x:v>45954.3935084954</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C209" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D209" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:4">
+      <x:c r="A210" s="1">
+        <x:v>45954.3935088542</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C210" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D210" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:4">
+      <x:c r="A211" s="1">
+        <x:v>45954.3935092245</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C211" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D211" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:4">
+      <x:c r="A212" s="1">
+        <x:v>45954.3935097685</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C212" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D212" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:4">
+      <x:c r="A213" s="1">
+        <x:v>45954.3935101273</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C213" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D213" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:4">
+      <x:c r="A214" s="1">
+        <x:v>45954.3935104977</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C214" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D214" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:4">
+      <x:c r="A215" s="1">
+        <x:v>45954.3935109143</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C215" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D215" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:4">
+      <x:c r="A216" s="1">
+        <x:v>45954.393511412</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C216" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D216" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:4">
+      <x:c r="A217" s="1">
+        <x:v>45954.3935117708</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C217" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D217" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:4">
+      <x:c r="A218" s="1">
+        <x:v>45954.3935121412</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C218" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D218" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:4">
+      <x:c r="A219" s="1">
+        <x:v>45954.3935125</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C219" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D219" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:4">
+      <x:c r="A220" s="1">
+        <x:v>45954.3935128704</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C220" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D220" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:4">
+      <x:c r="A221" s="1">
+        <x:v>45954.3935133218</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C221" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D221" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:4">
+      <x:c r="A222" s="1">
+        <x:v>45954.3935137731</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C222" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D222" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:4">
+      <x:c r="A223" s="1">
+        <x:v>45954.3935141782</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C223" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D223" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:4">
+      <x:c r="A224" s="1">
+        <x:v>45954.3935146875</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C224" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D224" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:4">
+      <x:c r="A225" s="1">
+        <x:v>45954.3935150579</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C225" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D225" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:4">
+      <x:c r="A226" s="1">
+        <x:v>45954.3935154167</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C226" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D226" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:4">
+      <x:c r="A227" s="1">
+        <x:v>45954.393515787</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C227" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D227" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:4">
+      <x:c r="A228" s="1">
+        <x:v>45954.3935161458</x:v>
+      </x:c>
+      <x:c r="B228" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C228" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D228" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:4">
+      <x:c r="A229" s="1">
+        <x:v>45954.3935165972</x:v>
+      </x:c>
+      <x:c r="B229" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C229" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D229" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:4">
+      <x:c r="A230" s="1">
+        <x:v>45954.3935170602</x:v>
+      </x:c>
+      <x:c r="B230" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C230" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D230" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:4">
+      <x:c r="A231" s="1">
+        <x:v>45954.393517419</x:v>
+      </x:c>
+      <x:c r="B231" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C231" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D231" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:4">
+      <x:c r="A232" s="1">
+        <x:v>45954.3935177894</x:v>
+      </x:c>
+      <x:c r="B232" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C232" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D232" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:4">
+      <x:c r="A233" s="1">
+        <x:v>45954.3935181482</x:v>
+      </x:c>
+      <x:c r="B233" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C233" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D233" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:4">
+      <x:c r="A234" s="1">
+        <x:v>45954.3935185185</x:v>
+      </x:c>
+      <x:c r="B234" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C234" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D234" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:4">
+      <x:c r="A235" s="1">
+        <x:v>45954.3935188773</x:v>
+      </x:c>
+      <x:c r="B235" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C235" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D235" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:4">
+      <x:c r="A236" s="1">
+        <x:v>45954.3935192593</x:v>
+      </x:c>
+      <x:c r="B236" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C236" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D236" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:4">
+      <x:c r="A237" s="1">
+        <x:v>45954.3935197917</x:v>
+      </x:c>
+      <x:c r="B237" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C237" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D237" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:4">
+      <x:c r="A238" s="1">
+        <x:v>45954.393520162</x:v>
+      </x:c>
+      <x:c r="B238" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C238" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D238" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:4">
+      <x:c r="A239" s="1">
+        <x:v>45954.3935206019</x:v>
+      </x:c>
+      <x:c r="B239" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C239" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D239" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:4">
+      <x:c r="A240" s="1">
+        <x:v>45954.3935210648</x:v>
+      </x:c>
+      <x:c r="B240" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C240" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D240" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:4">
+      <x:c r="A241" s="1">
+        <x:v>45954.3935214236</x:v>
+      </x:c>
+      <x:c r="B241" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C241" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D241" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:4">
+      <x:c r="A242" s="1">
+        <x:v>45954.3935217824</x:v>
+      </x:c>
+      <x:c r="B242" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C242" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D242" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:4">
+      <x:c r="A243" s="1">
+        <x:v>45954.3935225116</x:v>
+      </x:c>
+      <x:c r="B243" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C243" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D243" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:4">
+      <x:c r="A244" s="1">
+        <x:v>45954.3935228819</x:v>
+      </x:c>
+      <x:c r="B244" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C244" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D244" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:4">
+      <x:c r="A245" s="1">
+        <x:v>45954.3935232755</x:v>
+      </x:c>
+      <x:c r="B245" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C245" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D245" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:4">
+      <x:c r="A246" s="1">
+        <x:v>45954.3935236111</x:v>
+      </x:c>
+      <x:c r="B246" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C246" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D246" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:4">
+      <x:c r="A247" s="1">
+        <x:v>45954.3935239468</x:v>
+      </x:c>
+      <x:c r="B247" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C247" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D247" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:4">
+      <x:c r="A248" s="1">
+        <x:v>45954.3935243403</x:v>
+      </x:c>
+      <x:c r="B248" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C248" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D248" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:4">
+      <x:c r="A249" s="1">
+        <x:v>45954.3935246759</x:v>
+      </x:c>
+      <x:c r="B249" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C249" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D249" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:4">
+      <x:c r="A250" s="1">
+        <x:v>45954.3935250463</x:v>
+      </x:c>
+      <x:c r="B250" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C250" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D250" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:4">
+      <x:c r="A251" s="1">
+        <x:v>45954.3935254051</x:v>
+      </x:c>
+      <x:c r="B251" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C251" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D251" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:4">
+      <x:c r="A252" s="1">
+        <x:v>45954.3935257755</x:v>
+      </x:c>
+      <x:c r="B252" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C252" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D252" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:4">
+      <x:c r="A253" s="1">
+        <x:v>45954.3935261458</x:v>
+      </x:c>
+      <x:c r="B253" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C253" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D253" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:4">
+      <x:c r="A254" s="1">
+        <x:v>45954.3935265162</x:v>
+      </x:c>
+      <x:c r="B254" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C254" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D254" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:4">
+      <x:c r="A255" s="1">
+        <x:v>45954.393526875</x:v>
+      </x:c>
+      <x:c r="B255" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C255" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D255" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:4">
+      <x:c r="A256" s="1">
+        <x:v>45954.393527419</x:v>
+      </x:c>
+      <x:c r="B256" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C256" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D256" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:4">
+      <x:c r="A257" s="1">
+        <x:v>45954.3935277894</x:v>
+      </x:c>
+      <x:c r="B257" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C257" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D257" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:4">
+      <x:c r="A258" s="1">
+        <x:v>45954.3935281481</x:v>
+      </x:c>
+      <x:c r="B258" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C258" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D258" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:4">
+      <x:c r="A259" s="1">
+        <x:v>45954.3935285185</x:v>
+      </x:c>
+      <x:c r="B259" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C259" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D259" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:4">
+      <x:c r="A260" s="1">
+        <x:v>45954.3935288773</x:v>
+      </x:c>
+      <x:c r="B260" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C260" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D260" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:4">
+      <x:c r="A261" s="1">
+        <x:v>45954.3935292824</x:v>
+      </x:c>
+      <x:c r="B261" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C261" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D261" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:4">
+      <x:c r="A262" s="1">
+        <x:v>45954.3935296759</x:v>
+      </x:c>
+      <x:c r="B262" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C262" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D262" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:4">
+      <x:c r="A263" s="1">
+        <x:v>45954.393530162</x:v>
+      </x:c>
+      <x:c r="B263" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C263" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D263" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" spans="1:4">
+      <x:c r="A264" s="1">
+        <x:v>45954.3935305208</x:v>
+      </x:c>
+      <x:c r="B264" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C264" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D264" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:4">
+      <x:c r="A265" s="1">
+        <x:v>45954.3935308681</x:v>
+      </x:c>
+      <x:c r="B265" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C265" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D265" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:4">
+      <x:c r="A266" s="1">
+        <x:v>45954.3935312384</x:v>
+      </x:c>
+      <x:c r="B266" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C266" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D266" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:4">
+      <x:c r="A267" s="1">
+        <x:v>45954.3935315972</x:v>
+      </x:c>
+      <x:c r="B267" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C267" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D267" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:4">
+      <x:c r="A268" s="1">
+        <x:v>45954.3935319676</x:v>
+      </x:c>
+      <x:c r="B268" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C268" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D268" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:4">
+      <x:c r="A269" s="1">
+        <x:v>45954.3935324074</x:v>
+      </x:c>
+      <x:c r="B269" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C269" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D269" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:4">
+      <x:c r="A270" s="1">
+        <x:v>45954.3935328704</x:v>
+      </x:c>
+      <x:c r="B270" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C270" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D270" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:4">
+      <x:c r="A271" s="1">
+        <x:v>45954.3935332407</x:v>
+      </x:c>
+      <x:c r="B271" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C271" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D271" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:4">
+      <x:c r="A272" s="1">
+        <x:v>45954.3935335995</x:v>
+      </x:c>
+      <x:c r="B272" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C272" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D272" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:4">
+      <x:c r="A273" s="1">
+        <x:v>45954.3935339699</x:v>
+      </x:c>
+      <x:c r="B273" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C273" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D273" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:4">
+      <x:c r="A274" s="1">
+        <x:v>45954.3935343287</x:v>
+      </x:c>
+      <x:c r="B274" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C274" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D274" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:4">
+      <x:c r="A275" s="1">
+        <x:v>45954.3935346875</x:v>
+      </x:c>
+      <x:c r="B275" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C275" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D275" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:4">
+      <x:c r="A276" s="1">
+        <x:v>45954.3935350579</x:v>
+      </x:c>
+      <x:c r="B276" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C276" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D276" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:4">
+      <x:c r="A277" s="1">
+        <x:v>45954.3935356018</x:v>
+      </x:c>
+      <x:c r="B277" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C277" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D277" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:4">
+      <x:c r="A278" s="1">
+        <x:v>45954.3935359722</x:v>
+      </x:c>
+      <x:c r="B278" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C278" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D278" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:4">
+      <x:c r="A279" s="1">
+        <x:v>45954.393536331</x:v>
+      </x:c>
+      <x:c r="B279" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C279" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D279" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:4">
+      <x:c r="A280" s="1">
+        <x:v>45954.3935367014</x:v>
+      </x:c>
+      <x:c r="B280" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C280" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D280" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:4">
+      <x:c r="A281" s="1">
+        <x:v>45954.3935370602</x:v>
+      </x:c>
+      <x:c r="B281" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C281" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D281" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:4">
+      <x:c r="A282" s="1">
+        <x:v>45954.3935374653</x:v>
+      </x:c>
+      <x:c r="B282" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C282" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D282" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:4">
+      <x:c r="A283" s="1">
+        <x:v>45954.3935378009</x:v>
+      </x:c>
+      <x:c r="B283" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C283" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D283" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:4">
+      <x:c r="A284" s="1">
+        <x:v>45954.3935381597</x:v>
+      </x:c>
+      <x:c r="B284" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C284" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D284" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:4">
+      <x:c r="A285" s="1">
+        <x:v>45954.3935385301</x:v>
+      </x:c>
+      <x:c r="B285" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C285" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D285" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:4">
+      <x:c r="A286" s="1">
+        <x:v>45954.3935388889</x:v>
+      </x:c>
+      <x:c r="B286" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C286" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D286" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:4">
+      <x:c r="A287" s="1">
+        <x:v>45954.3935393403</x:v>
+      </x:c>
+      <x:c r="B287" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C287" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D287" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:4">
+      <x:c r="A288" s="1">
+        <x:v>45954.3935398032</x:v>
+      </x:c>
+      <x:c r="B288" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C288" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D288" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:4">
+      <x:c r="A289" s="1">
+        <x:v>45954.3935401852</x:v>
+      </x:c>
+      <x:c r="B289" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C289" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D289" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:4">
+      <x:c r="A290" s="1">
+        <x:v>45954.3935405324</x:v>
+      </x:c>
+      <x:c r="B290" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C290" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D290" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:4">
+      <x:c r="A291" s="1">
+        <x:v>45954.3935408912</x:v>
+      </x:c>
+      <x:c r="B291" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C291" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D291" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:4">
+      <x:c r="A292" s="1">
+        <x:v>45954.393541331</x:v>
+      </x:c>
+      <x:c r="B292" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C292" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D292" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:4">
+      <x:c r="A293" s="1">
+        <x:v>45954.3935418056</x:v>
+      </x:c>
+      <x:c r="B293" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C293" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D293" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:4">
+      <x:c r="A294" s="1">
+        <x:v>45954.3935423495</x:v>
+      </x:c>
+      <x:c r="B294" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C294" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D294" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:4">
+      <x:c r="A295" s="1">
+        <x:v>45954.3935427315</x:v>
+      </x:c>
+      <x:c r="B295" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C295" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D295" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:4">
+      <x:c r="A296" s="1">
+        <x:v>45954.3935430787</x:v>
+      </x:c>
+      <x:c r="B296" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C296" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D296" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:4">
+      <x:c r="A297" s="1">
+        <x:v>45954.3935436343</x:v>
+      </x:c>
+      <x:c r="B297" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C297" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D297" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:4">
+      <x:c r="A298" s="1">
+        <x:v>45954.3935439931</x:v>
+      </x:c>
+      <x:c r="B298" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C298" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D298" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:4">
+      <x:c r="A299" s="1">
+        <x:v>45954.3935444097</x:v>
+      </x:c>
+      <x:c r="B299" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C299" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D299" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:4">
+      <x:c r="A300" s="1">
+        <x:v>45954.3935448958</x:v>
+      </x:c>
+      <x:c r="B300" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C300" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D300" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:4">
+      <x:c r="A301" s="1">
+        <x:v>45954.3935452546</x:v>
+      </x:c>
+      <x:c r="B301" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C301" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D301" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:4">
+      <x:c r="A302" s="1">
+        <x:v>45954.3935456366</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D302" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:4">
+      <x:c r="A303" s="1">
+        <x:v>45954.3935459838</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D303" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:4">
+      <x:c r="A304" s="1">
+        <x:v>45954.3935465278</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D304" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
